--- a/Reinfection_Augments_Heterogeneity/Public/Results/Mean Pathogen Load and Pathology/combined_tes_lquant_sec_kruskal_dunn.xlsx
+++ b/Reinfection_Augments_Heterogeneity/Public/Results/Mean Pathogen Load and Pathology/combined_tes_lquant_sec_kruskal_dunn.xlsx
@@ -538,49 +538,49 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>High - Low</t>
+          <t>High Priming - Low Priming</t>
         </is>
       </c>
       <c r="B2">
-        <v>-1.264480872688328</v>
+        <v>-1.932183566158592</v>
       </c>
       <c r="C2">
-        <v>0.1030287408727286</v>
+        <v>0.0266684264145699</v>
       </c>
       <c r="D2">
-        <v>0.3090862226181858</v>
+        <v>0.0800052792437097</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>High - Sham</t>
+          <t>High Priming - Sham Priming</t>
         </is>
       </c>
       <c r="B3">
-        <v>-3.593787743429985</v>
+        <v>-2.102476673655455</v>
       </c>
       <c r="C3">
-        <v>0.0001629526820107044</v>
+        <v>0.01775577045093267</v>
       </c>
       <c r="D3">
-        <v>0.0004888580460321132</v>
+        <v>0.053267311352798</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Low - Sham</t>
+          <t>Low Priming - Sham Priming</t>
         </is>
       </c>
       <c r="B4">
-        <v>-2.442997656137377</v>
+        <v>-0.05634361698190091</v>
       </c>
       <c r="C4">
-        <v>0.007282915940124626</v>
+        <v>0.4775340363368423</v>
       </c>
       <c r="D4">
-        <v>0.02184874782037388</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
